--- a/app/teste/tmp/relatorio_executivo_ecd_efd_1_4_202211.xlsx
+++ b/app/teste/tmp/relatorio_executivo_ecd_efd_1_4_202211.xlsx
@@ -8,26 +8,27 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BasesEfdPorNatureza" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CoberturaPorMes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlertasEfdOmissao" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DiagnosticoEfd-ECD" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DetalheCompleto" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alertas Efd Omissao" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bases Por Natureza" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura Por Mes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnostico Entrada" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalhe Completo" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investigar" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CombustiveisLubrificantes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnergiaEletricaOperacional" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CorrecoesAutomaticas" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAT_ServicosTerceirosOperacio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAT_EnergiaEletricaOperaciona" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAT_CombustiveisLubrificantes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CorrecoesAutomaticas" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BasesEfdPorNatureza'!$A$2:$D$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CoberturaPorMes'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AlertasEfdOmissao'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DiagnosticoEfd-ECD'!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DetalheCompleto'!$A$1:$Q$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Investigar'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'CombustiveisLubrificantes'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'EnergiaEletricaOperacional'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CorrecoesAutomaticas'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alertas Efd Omissao'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bases Por Natureza'!$A$2:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cobertura Por Mes'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Detalhe Completo'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Investigar'!$A$1:$L$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'CAT_ServicosTerceirosOperacio'!$A$3:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'CAT_EnergiaEletricaOperaciona'!$A$3:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CAT_CombustiveisLubrificantes'!$A$3:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'CorrecoesAutomaticas'!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,6 +50,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
@@ -56,19 +61,25 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F7F7"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -92,12 +103,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7F7F7"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,11 +114,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
     </border>
     <border>
       <left style="thin">
@@ -128,39 +129,47 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -659,100 +668,294 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>385468.12</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>5158.37</v>
-      </c>
-      <c r="C6" s="5" t="n">
+      <c r="B7" s="5" t="n">
+        <v>390626.49</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>2500</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D7" s="5" t="n">
         <v>2658.37</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E7" s="5" t="n">
         <v>43.86</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>202.04</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>245.9</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Notas Metodológicas</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1. Base ECD representa despesas elegíveis classificadas por categoria contábil.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2. Gap Identificado representa potencial ainda sujeito à validação fiscal.</t>
+          <t>1. Base ECD representa despesas elegíveis classificadas por categoria contábil.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3. Crédito potencial calculado com PIS 1,65% e COFINS 7,60% nesta versão inicial.</t>
+          <t>2. Gap Identificado representa potencial ainda sujeito à validação fiscal.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4. Bases por natureza e divergências técnicas constam nas abas específicas.</t>
+          <t>3. Crédito potencial calculado com PIS 1,65% e COFINS 7,60% nesta versão inicial.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5. Itens sem lastro suficiente devem ser revisados na aba Investigar.</t>
+          <t>4. Bases por natureza e divergências técnicas constam nas abas específicas.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>5. Itens sem lastro suficiente devem ser revisados na aba Investigar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>6. A Base Atribuída EFD é rateada proporcionalmente entre as categorias elegíveis para fins de estimativa executiva.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ALERTA - Apenas 48.46% da despesa elegível identificada na ECD possui lastro declarado na EFD-Contribuições.</t>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>⚠ ALERTA - 1 mês(es) com EFD entregue zerada e despesa elegível na ECD: 202211. Crédito perdido estimado: R$ 5,158.37. Ver aba 'Alertas EFD Omissão'.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A17:G17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="80" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Categoria: Combustiveis Lubrificantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Fundamento: Essencialidade | Naturezas Esperadas: 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Código Conta</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Fundamento</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Naturezas Esperadas</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Despesa Contábil</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Crédito PIS</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Crédito COFINS</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>Observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>COMBUSTÍVEL</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>COMBUSTIVEL_LUBRIFICANTE</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Essencialidade</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>342</v>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>Insumo motriz - REsp 1.221.170/PR. Segregar consumo da frota operacional do consumo administrativo.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:N4"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -769,27 +972,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Regra</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Tipo de correção</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Impacto financeiro</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Automatizável?</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -802,332 +1005,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bases declaradas na EFD-Contribuições por mês e natureza</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Ano-Mês</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Cód.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Natureza</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Base Declarada</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Aquisição de bens para revenda</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Aquisição de bens utilizados como insumo</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Aquisição de serviços utilizados como insumo</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Energia elétrica e térmica, inclusive sob a forma de vapor</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Mismatches detectados (categoria ECD com classificação vs naturezas EFD esperadas)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Categoria ECD</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Despesa elegível ECD</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Naturezas EFD esperadas</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Base declarada nessas naturezas</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CombustiveisLubrificantes</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ServicosTerceirosOperacionais</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>638</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>EnergiaEletricaOperacional</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Linhas destacam categorias classificadas na ECD e a cobertura encontrada nas naturezas de crédito esperadas da EFD-Contribuições.</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:D6"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A7:D7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="64" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Período</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>ECD Elegível</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>EFD Declarada</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>GAP</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>Cobertura %</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>Interpretação</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="n">
-        <v>5158.37</v>
-      </c>
-      <c r="C2" s="12" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D2" s="12" t="n">
-        <v>2658.37</v>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>BAIXA_COBERTURA</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>A EFD declarou 48.46% da despesa elegível identificada na ECD.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1149,184 +1026,184 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Período</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Tipo Alerta</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>NAT_BC_CRED</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>ECD Elegível</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>EFD Declarada</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>GAP</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Cobertura %</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Status Natureza</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>EFD_ZERADA_COM_DESPESA_ECD</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>CombustiveisLubrificantes</t>
         </is>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="9" t="n">
         <v>4500</v>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="11" t="n">
+      <c r="F2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9" t="n">
         <v>4500</v>
       </c>
-      <c r="H2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="H2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>SEM_EFD</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>Existe despesa elegível na ECD, mas nenhuma base correspondente foi declarada na EFD.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>EFD_ZERADA_COM_DESPESA_ECD</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>ServicosTerceirosOperacionais</t>
         </is>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="10" t="n">
         <v>638</v>
       </c>
-      <c r="F3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="13" t="n">
+      <c r="F3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10" t="n">
         <v>638</v>
       </c>
-      <c r="H3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="H3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>SEM_EFD</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Existe despesa elegível na ECD, mas nenhuma base correspondente foi declarada na EFD.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>EFD_ZERADA_COM_DESPESA_ECD</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>EnergiaEletricaOperacional</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="9" t="n">
         <v>20.37</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="11" t="n">
+      <c r="F4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9" t="n">
         <v>20.37</v>
       </c>
-      <c r="H4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="H4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>SEM_EFD</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Existe despesa elegível na ECD, mas nenhuma base correspondente foi declarada na EFD.</t>
         </is>
@@ -1334,6 +1211,332 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bases declaradas na EFD-Contribuições por mês e natureza</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ano-Mês</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Cód.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Natureza</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Base Declarada</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Aquisição de bens para revenda</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Aquisição de bens utilizados como insumo</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Aquisição de serviços utilizados como insumo</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Energia elétrica e térmica, inclusive sob a forma de vapor</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Mismatches detectados (categoria ECD com classificação vs naturezas EFD esperadas)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Categoria ECD</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Despesa elegível ECD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Naturezas EFD esperadas</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Base declarada nessas naturezas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CombustiveisLubrificantes</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ServicosTerceirosOperacionais</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>638</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EnergiaEletricaOperacional</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Linhas destacam categorias classificadas na ECD e a cobertura encontrada nas naturezas de crédito esperadas da EFD-Contribuições.</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A7:D7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>ECD Elegível</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>EFD Declarada</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Cobertura %</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Interpretação</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="n">
+        <v>5158.37</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>2658.37</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>BAIXA_COBERTURA</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>A EFD declarou 48.46% da despesa elegível identificada na ECD.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1344,251 +1547,258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Período</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>NAT_BC_CRED</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Diagnóstico de Entrada — qualidade do plano de contas e da classificação</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Contas com despesa no período</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linhas geradas (conta x mês)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Contas classificadas (heurística OU override)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Contas em 'Investigar' (sem match)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>% de cobertura da classificação</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Classificadas via override CSV</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Classificadas via heurística</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Confiança média da classificação</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>81.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Contas com confiança &lt; 70% (revisar)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Meses cobertos na ECD</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meses cobertos na EFD</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Falhas de leitura de arquivos</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Distribuição por categoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>ECD Elegível</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>EFD Declarada</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>GAP</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>Cobertura %</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>Prioridade</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>Diagnóstico</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>EFD NAT 01 - sem categoria ECD</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>SEM_ECD</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="J2" s="11" t="inlineStr">
-        <is>
-          <t>Base declarada na EFD sem despesa elegível correspondente identificada na ECD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Contas distintas</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Despesa total</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>CombustiveisLubrificantes</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>4500</v>
       </c>
-      <c r="E3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13" t="n">
+      <c r="D20" s="3" t="n">
         <v>4500</v>
       </c>
-      <c r="G3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>SEM_EFD</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>ServicosTerceirosOperacionais</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>638</v>
       </c>
-      <c r="E4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
+      <c r="D21" s="3" t="n">
         <v>638</v>
       </c>
-      <c r="G4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>SEM_EFD</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>202211</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>EnergiaEletricaOperacional</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>20.37</v>
       </c>
-      <c r="E5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13" t="n">
+      <c r="D22" s="3" t="n">
         <v>20.37</v>
       </c>
-      <c r="G5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>SEM_EFD</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
-        </is>
-      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>385468.12</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1599,7 +1809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1615,401 +1825,1339 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="80" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Ano-Mês</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Código Conta</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>NAT_BC_CRED</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Fundamento</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Naturezas Esperadas</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Despesa Contábil</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Base Atribuída</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Gap Atribuído</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>Crédito PIS</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>Crédito COFINS</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Fonte</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr"/>
+      <c r="I2" s="13" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O2" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P2" s="9" t="inlineStr"/>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>325</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>SERVIÇOS PRESTADOS POR TERCEIROS</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>ServicosTerceirosOperacionais</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>SERVICOS_TERCEIROS</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Essencialidade</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I3" s="14" t="n">
         <v>396</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J3" s="14" t="n">
         <v>396</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K3" s="14" t="n">
         <v>396</v>
       </c>
-      <c r="L2" s="12" t="n">
+      <c r="L3" s="14" t="n">
         <v>6.53</v>
       </c>
-      <c r="M2" s="12" t="n">
+      <c r="M3" s="14" t="n">
         <v>30.1</v>
       </c>
-      <c r="N2" s="11" t="inlineStr">
-        <is>
-          <t>I355</t>
-        </is>
-      </c>
-      <c r="O2" s="11" t="n">
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P3" s="10" t="inlineStr">
         <is>
           <t>SEM_EFD</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>Serviço prestado por terceiros. Verificar se está vinculado à atividade operacional e se há documento fiscal hábil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>SALÁRIOS E ORDENADOS</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr"/>
+      <c r="I4" s="13" t="n">
+        <v>4837.64</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>4837.64</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" s="9" t="inlineStr"/>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="14" t="n">
+        <v>1212</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>1212</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>13º SALÁRIO</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="13" t="n">
+        <v>403.11</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>403.11</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P6" s="9" t="inlineStr"/>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>FÉRIAS</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr"/>
+      <c r="I7" s="14" t="n">
+        <v>537.49</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>537.49</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P7" s="10" t="inlineStr"/>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="13" t="n">
+        <v>1868.25</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>1868.25</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P8" s="9" t="inlineStr"/>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>FGTS</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="14" t="n">
+        <v>462.25</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>462.25</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P9" s="10" t="inlineStr"/>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>PARCELAMENTO FEDERAL</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="13" t="n">
+        <v>829.9</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>829.9</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P10" s="9" t="inlineStr"/>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>354</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>ENERGIA ELÉTRICA</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>EnergiaEletricaOperacional</t>
         </is>
       </c>
-      <c r="F3" s="13" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>ENERGIA_OPERACIONAL</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Essencialidade</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="I3" s="14" t="n">
+      <c r="I11" s="14" t="n">
         <v>20.37</v>
       </c>
-      <c r="J3" s="14" t="n">
+      <c r="J11" s="14" t="n">
         <v>20.37</v>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="K11" s="14" t="n">
         <v>20.37</v>
       </c>
-      <c r="L3" s="14" t="n">
+      <c r="L11" s="14" t="n">
         <v>0.34</v>
       </c>
-      <c r="M3" s="14" t="n">
+      <c r="M11" s="14" t="n">
         <v>1.55</v>
       </c>
-      <c r="N3" s="13" t="inlineStr">
-        <is>
-          <t>I355</t>
-        </is>
-      </c>
-      <c r="O3" s="13" t="n">
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P11" s="10" t="inlineStr">
         <is>
           <t>SEM_EFD</t>
         </is>
       </c>
-      <c r="Q3" s="13" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>SC COSIT 204/2021 e 6.032/2021 - apenas kWh efetivamente consumido. Excluir iluminação pública e taxas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ÁGUA E ESGOTO</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="13" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P12" s="9" t="inlineStr"/>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>ASSISTÊNCIA CONTÁBIL</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr"/>
+      <c r="I13" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P13" s="10" t="inlineStr"/>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>362</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS PRESTADOS POR TERCEIROS</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>ServicosTerceirosOperacionais</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>SERVICOS_TERCEIROS</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Essencialidade</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I14" s="13" t="n">
         <v>242</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J14" s="13" t="n">
         <v>242</v>
       </c>
-      <c r="K4" s="12" t="n">
+      <c r="K14" s="13" t="n">
         <v>242</v>
       </c>
-      <c r="L4" s="12" t="n">
+      <c r="L14" s="13" t="n">
         <v>3.99</v>
       </c>
-      <c r="M4" s="12" t="n">
+      <c r="M14" s="13" t="n">
         <v>18.39</v>
       </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>I355</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="n">
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="n">
         <v>70</v>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>SEM_EFD</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>Serviço prestado por terceiros. Verificar se está vinculado à atividade operacional e se há documento fiscal hábil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>292</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>COMBUSTÍVEL</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>CombustiveisLubrificantes</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>COMBUSTIVEL_LUBRIFICANTE</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Essencialidade</t>
         </is>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="I15" s="14" t="n">
         <v>4500</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J15" s="14" t="n">
         <v>4500</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K15" s="14" t="n">
         <v>4500</v>
       </c>
-      <c r="L5" s="14" t="n">
+      <c r="L15" s="14" t="n">
         <v>74.25</v>
       </c>
-      <c r="M5" s="14" t="n">
+      <c r="M15" s="14" t="n">
         <v>342</v>
       </c>
-      <c r="N5" s="13" t="inlineStr">
-        <is>
-          <t>I355</t>
-        </is>
-      </c>
-      <c r="O5" s="13" t="n">
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="P5" s="13" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>SEM_EFD</t>
         </is>
       </c>
-      <c r="Q5" s="13" t="inlineStr">
-        <is>
-          <t>Insumo operacional sujeito à segregação entre uso operacional e administrativo.</t>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>Insumo motriz - REsp 1.221.170/PR. Segregar consumo da frota operacional do consumo administrativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>VENDA DE MERCADORIAS</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="13" t="n">
+        <v>214628</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>214628</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P16" s="9" t="inlineStr"/>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>(-) CONTRIBUIÇÃO SOCIAL</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr"/>
+      <c r="I17" s="14" t="n">
+        <v>2904.26</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>2904.26</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P17" s="10" t="inlineStr"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>(-) IMPOSTO DE RENDA</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="13" t="n">
+        <v>4840.43</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>4840.43</v>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P18" s="9" t="inlineStr"/>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>CUSTOS DAS MERCADORIAS VENDIDAS</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr"/>
+      <c r="I19" s="14" t="n">
+        <v>122776.16</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>122776.16</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P19" s="10" t="inlineStr"/>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q5"/>
+  <autoFilter ref="A1:Q19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2020,269 +3168,899 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="80" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="69" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Período</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Prioridade</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>NAT_BC_CRED</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Código Conta</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Despesa Contábil</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>Contas</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>ECD Elegível</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>EFD Declarada</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>GAP</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>Cobertura %</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="K1" s="10" t="inlineStr">
-        <is>
-          <t>Diagnóstico</t>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Fundamento</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Origem Valor</t>
+        </is>
+      </c>
+      <c r="K1" s="8" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="L1" s="8" t="inlineStr">
+        <is>
+          <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr"/>
-      <c r="E2" s="11" t="inlineStr"/>
-      <c r="F2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H2" s="11" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="I2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="11" t="inlineStr">
-        <is>
-          <t>SEM_ECD</t>
-        </is>
-      </c>
-      <c r="K2" s="11" t="inlineStr">
-        <is>
-          <t>Base declarada na EFD sem despesa elegível correspondente identificada na ECD.</t>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>TELEFONE</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>CombustiveisLubrificantes</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>4500</v>
-      </c>
-      <c r="I3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>SEM_EFD</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>SALÁRIOS E ORDENADOS</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>4837.64</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>ServicosTerceirosOperacionais</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>325, 362</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>638</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>638</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>SEM_EFD</t>
-        </is>
-      </c>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>PRÓ-LABORE</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>EnergiaEletricaOperacional</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>SEM_EFD</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>Despesa elegível identificada na ECD, mas sem base correspondente declarada na EFD.</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>13º SALÁRIO</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>403.11</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>FÉRIAS</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>537.49</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>1868.25</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>FGTS</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>462.25</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>PARCELAMENTO FEDERAL</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>829.9</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>ÁGUA E ESGOTO</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>ASSISTÊNCIA CONTÁBIL</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>VENDA DE MERCADORIAS</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>214628</v>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>(-) CONTRIBUIÇÃO SOCIAL</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>2904.26</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>(-) IMPOSTO DE RENDA</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>4840.43</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>CUSTOS DAS MERCADORIAS VENDIDAS</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>122776.16</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>NaoClassificado</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>NAO_CLASSIFICADO</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Investigar</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>I355</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>Conta sem correspondência em categoria elegível do catálogo fiscal.</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>Classificação sem correspondência no catálogo fiscal.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:L15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2293,143 +4071,237 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Ano-Mês</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Categoria: Servicos Terceiros Operacionais</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Fundamento: Essencialidade | Naturezas Esperadas: 03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Código Conta</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Fundamento</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Naturezas Esperadas</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Despesa Contábil</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>Base Atribuída</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>Gap Atribuído</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Crédito PIS</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Crédito COFINS</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
-        <is>
-          <t>Total Recuperável</t>
-        </is>
-      </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Fonte</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>COMBUSTÍVEL</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>CombustiveisLubrificantes</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>SERVICOS_TERCEIROS</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Essencialidade</t>
         </is>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G2" s="11" t="inlineStr"/>
-      <c r="H2" s="11" t="inlineStr"/>
-      <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="11" t="inlineStr"/>
-      <c r="K2" s="11" t="inlineStr"/>
-      <c r="L2" s="11" t="inlineStr">
-        <is>
-          <t>I355</t>
-        </is>
-      </c>
-      <c r="M2" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="N2" s="11" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>396</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>396</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>396</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>Serviço prestado por terceiros. Verificar se está vinculado à atividade operacional e se há documento fiscal hábil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>202211</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>SERVIÇOS PRESTADOS POR TERCEIROS</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>SERVICOS_TERCEIROS</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Essencialidade</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>242</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>242</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>242</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>Serviço prestado por terceiros. Verificar se está vinculado à atividade operacional e se há documento fiscal hábil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A3:N5"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2440,143 +4312,177 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="80" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Ano-Mês</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Categoria: Energia Eletrica Operacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Fundamento: Essencialidade | Naturezas Esperadas: 04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Código Conta</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Fundamento</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Naturezas Esperadas</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Despesa Contábil</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>Base Atribuída</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>Gap Atribuído</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Crédito PIS</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Crédito COFINS</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
-        <is>
-          <t>Total Recuperável</t>
-        </is>
-      </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Fonte</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>354</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>ENERGIA ELÉTRICA</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>EnergiaEletricaOperacional</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>ENERGIA_OPERACIONAL</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Essencialidade</t>
         </is>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="n">
         <v>20.37</v>
       </c>
-      <c r="G2" s="11" t="inlineStr"/>
-      <c r="H2" s="11" t="inlineStr"/>
-      <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="11" t="inlineStr"/>
-      <c r="K2" s="11" t="inlineStr"/>
-      <c r="L2" s="11" t="inlineStr">
-        <is>
-          <t>I355</t>
-        </is>
-      </c>
-      <c r="M2" s="11" t="n">
+      <c r="H4" s="13" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Heurística</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="N2" s="11" t="inlineStr"/>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>SC COSIT 204/2021 e 6.032/2021 - apenas kWh efetivamente consumido. Excluir iluminação pública e taxas.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A3:N4"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>